--- a/assets/templates/template-marketing.xlsx
+++ b/assets/templates/template-marketing.xlsx
@@ -1220,7 +1220,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3. الأعمدة النصية (القناة، الحملة) تصير فلاتر وتقسيمات في الداش بورد.</v>
+        <v>3. الأعمدة النصية (القناة، الحملة) تصير فلاتر وتقسيمات في لوحة التحكم.</v>
       </c>
     </row>
     <row r="6">

--- a/assets/templates/template-marketing.xlsx
+++ b/assets/templates/template-marketing.xlsx
@@ -1220,7 +1220,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3. الأعمدة النصية (القناة، الحملة) تصير فلاتر وتقسيمات في لوحة التحكم.</v>
+        <v>3. الأعمدة النصية (القناة، الحملة) تصير فلاتر وتقسيمات في لوحة المؤشرات.</v>
       </c>
     </row>
     <row r="6">
